--- a/data/trans_orig/IP31KM09_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM09_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31874</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28100</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34266</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36849</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32135</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40163</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>33920</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75192</t>
+          <t>65794</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80456</t>
+          <t>70185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9335</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9646</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6332</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14360</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146896</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>140549</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>150794</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>89,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>145902</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>139397</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>151000</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170394</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163889</t>
+          <t>125247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175039</t>
+          <t>137356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>316297</t>
+          <t>279610</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307954</t>
+          <t>271718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322837</t>
+          <t>286155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10146</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16493</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13397</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19902</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>190281</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>183315</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>195193</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>164505</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>158679</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>168621</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>202525</t>
+          <t>165762</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195572</t>
+          <t>159368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207675</t>
+          <t>169823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>367031</t>
+          <t>356043</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358851</t>
+          <t>347706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373445</t>
+          <t>362592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>267806</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>239207</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>278894</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>260120</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>252724</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>266941</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>278046</t>
+          <t>240752</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>233323</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>290771</t>
+          <t>246434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>538167</t>
+          <t>508558</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>500349</t>
+          <t>477025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>553471</t>
+          <t>520553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24415</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53014</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>14147</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7326</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21543</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71676</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>39000</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78917</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>636857</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>607353</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>650829</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>844</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>607377</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>594531</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>618007</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>643635</t>
+          <t>561227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>704732</t>
+          <t>582761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1256992</t>
+          <t>1181271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1314187</t>
+          <t>1226927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35995</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>79471</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>35127</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58603</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>35447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83680</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
